--- a/港岛-赤柱-海天径 1号, 舂磡角道 44, 46, 48, 50号/海天径 1号, 舂磡角道 44, 46, 48, 50号_销控明细表.xlsx
+++ b/港岛-赤柱-海天径 1号, 舂磡角道 44, 46, 48, 50号/海天径 1号, 舂磡角道 44, 46, 48, 50号_销控明细表.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -818,7 +818,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>舂磡角道46号</t>
+          <t>舂磡角道48号</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>4254</v>
+        <v>6350</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>舂磡角道48号</t>
+          <t>舂磡角道50号</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr"/>
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6350</v>
+        <v>6364</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -942,72 +942,6 @@
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>舂磡角道50号</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>6364</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1036,7 +970,6 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1081,7 +1014,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>5 套</t>
+          <t>4 套</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
@@ -1106,7 +1039,7 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>5 套</t>
+          <t>4 套</t>
         </is>
       </c>
     </row>
@@ -1128,15 +1061,10 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>舂磡角道46号</t>
+          <t>舂磡角道48号</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>舂磡角道48号</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>舂磡角道50号</t>
         </is>
@@ -1168,15 +1096,6 @@
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>舂磡角道46号
-4254呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
           <t>舂磡角道48号
 6350呎 (4+房)
 (待售)
@@ -1184,7 +1103,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>舂磡角道50号
 6364呎 (4+房)
@@ -1196,7 +1115,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/港岛-赤柱-海天径 1号, 舂磡角道 44, 46, 48, 50号/海天径 1号, 舂磡角道 44, 46, 48, 50号_销控明细表.xlsx
+++ b/港岛-赤柱-海天径 1号, 舂磡角道 44, 46, 48, 50号/海天径 1号, 舂磡角道 44, 46, 48, 50号_销控明细表.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -818,7 +818,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>舂磡角道48号</t>
+          <t>舂磡角道46号</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>6350</v>
+        <v>4254</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>舂磡角道50号</t>
+          <t>舂磡角道48号</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr"/>
@@ -899,49 +899,115 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
+        <v>6350</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>舂磡角道50号</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>6364</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>待售</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -970,6 +1036,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1014,7 +1081,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>4 套</t>
+          <t>5 套</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
@@ -1039,7 +1106,7 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>4 套</t>
+          <t>5 套</t>
         </is>
       </c>
     </row>
@@ -1061,10 +1128,15 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>舂磡角道46号</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>舂磡角道48号</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>舂磡角道50号</t>
         </is>
@@ -1096,6 +1168,15 @@
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
+          <t>舂磡角道46号
+4254呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
           <t>舂磡角道48号
 6350呎 (4+房)
 (待售)
@@ -1103,7 +1184,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>舂磡角道50号
 6364呎 (4+房)
@@ -1115,7 +1196,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/港岛-赤柱-海天径 1号, 舂磡角道 44, 46, 48, 50号/海天径 1号, 舂磡角道 44, 46, 48, 50号_销控明细表.xlsx
+++ b/港岛-赤柱-海天径 1号, 舂磡角道 44, 46, 48, 50号/海天径 1号, 舂磡角道 44, 46, 48, 50号_销控明细表.xlsx
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>4238</v>
+        <v>4405</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>4215</v>
+        <v>4374</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>4254</v>
+        <v>4375</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6350</v>
+        <v>6600</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6364</v>
+        <v>6615</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
       <c r="B6" s="15" t="inlineStr">
         <is>
           <t>海天径1号
-4238呎 (4+房)
+4405呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -1160,7 +1160,7 @@
       <c r="C6" s="15" t="inlineStr">
         <is>
           <t>舂磡角道44号
-4215呎 (4+房)
+4374呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -1169,7 +1169,7 @@
       <c r="D6" s="15" t="inlineStr">
         <is>
           <t>舂磡角道46号
-4254呎 (4+房)
+4375呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -1178,7 +1178,7 @@
       <c r="E6" s="15" t="inlineStr">
         <is>
           <t>舂磡角道48号
-6350呎 (4+房)
+6600呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -1187,7 +1187,7 @@
       <c r="F6" s="15" t="inlineStr">
         <is>
           <t>舂磡角道50号
-6364呎 (4+房)
+6615呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
